--- a/test-data/datos_prueba.xlsx
+++ b/test-data/datos_prueba.xlsx
@@ -116,10 +116,10 @@
     <t>110111</t>
   </si>
   <si>
-    <t>30814</t>
-  </si>
-  <si>
-    <t>2026-06-02T16:57:20.109Z</t>
+    <t>30820</t>
+  </si>
+  <si>
+    <t>2026-06-03T01:56:58.494Z</t>
   </si>
 </sst>
 </file>

--- a/test-data/datos_prueba.xlsx
+++ b/test-data/datos_prueba.xlsx
@@ -116,10 +116,10 @@
     <t>110111</t>
   </si>
   <si>
-    <t>30820</t>
-  </si>
-  <si>
-    <t>2026-06-03T01:56:58.494Z</t>
+    <t>30829</t>
+  </si>
+  <si>
+    <t>2026-06-04T15:45:04.566Z</t>
   </si>
 </sst>
 </file>

--- a/test-data/datos_prueba.xlsx
+++ b/test-data/datos_prueba.xlsx
@@ -116,10 +116,10 @@
     <t>110111</t>
   </si>
   <si>
-    <t>30829</t>
-  </si>
-  <si>
-    <t>2026-06-04T15:45:04.566Z</t>
+    <t>30833</t>
+  </si>
+  <si>
+    <t>2026-06-04T16:50:24.864Z</t>
   </si>
 </sst>
 </file>
